--- a/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_D1_otu_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_D1_otu_table.xlsx
@@ -12,11 +12,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">MS_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_003</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_004</t>
   </si>
   <si>
@@ -41,12 +47,21 @@
     <t xml:space="preserve">MS_025</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_027</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_028</t>
   </si>
   <si>
     <t xml:space="preserve">MS_030</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_032</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_035</t>
   </si>
   <si>
@@ -59,6 +74,9 @@
     <t xml:space="preserve">MS_038</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_039</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_040</t>
   </si>
   <si>
@@ -80,6 +98,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -101,12 +125,39 @@
     <t xml:space="preserve">MS_072</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_090</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_091</t>
   </si>
   <si>
     <t xml:space="preserve">MS_092</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_100</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_101</t>
   </si>
   <si>
@@ -158,6 +209,9 @@
     <t xml:space="preserve">MS_137</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_138</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_141</t>
   </si>
   <si>
@@ -173,6 +227,9 @@
     <t xml:space="preserve">MS_146</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_153</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_155</t>
   </si>
   <si>
@@ -203,6 +260,9 @@
     <t xml:space="preserve">MS_166</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_168</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_169</t>
   </si>
   <si>
@@ -323,6 +383,9 @@
     <t xml:space="preserve">MS_264</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_265</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_266</t>
   </si>
   <si>
@@ -332,6 +395,9 @@
     <t xml:space="preserve">MS_268</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_269</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_271</t>
   </si>
   <si>
@@ -341,25 +407,34 @@
     <t xml:space="preserve">MS_273</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_23</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_31</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_34</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_5</t>
@@ -1034,19 +1109,85 @@
       <c r="DE1" t="s">
         <v>108</v>
       </c>
+      <c r="DF1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>120</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>121</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>122</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>123</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>124</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>126</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>127</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>128</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1863</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1055,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1064,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2809</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2810</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1148,13 +1289,13 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>861</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1166,13 +1307,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2593</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -1361,27 +1502,93 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1694</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1590</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>30</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>83</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>2753</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1423,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1432,16 +1639,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1462,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -1483,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>2832</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1495,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -1504,16 +1711,16 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1925</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1639</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -1525,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1561,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>2730</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -1573,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>2126</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1612,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
@@ -1645,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -1654,19 +1861,19 @@
         <v>0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -1690,12 +1897,78 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>225</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>402</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>69</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>95</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -1710,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1719,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1749,37 +2022,37 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1788,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1809,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1839,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1863,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1881,16 +2154,16 @@
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1908,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
@@ -1926,73 +2199,73 @@
         <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="CI4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
@@ -2010,30 +2283,96 @@
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
       </c>
       <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1856</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2066,28 +2405,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -2108,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -2120,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2156,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
@@ -2168,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -2225,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2348,33 +2687,99 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>43</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>167</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>94</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2395,34 +2800,34 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2443,16 +2848,16 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -2470,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -2599,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
@@ -2677,12 +3082,78 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -2742,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -2790,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2811,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -2856,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="BI7" t="n">
         <v>0</v>
@@ -2895,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
@@ -2940,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
@@ -2955,10 +3426,10 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
@@ -2991,135 +3462,201 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>777</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>212</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>330</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>147</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI8" t="n">
         <v>115</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3128,10 +3665,10 @@
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -3149,22 +3686,22 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -3176,10 +3713,10 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -3209,22 +3746,22 @@
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -3236,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="BY8" t="n">
         <v>0</v>
@@ -3254,19 +3791,19 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="CE8" t="n">
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
@@ -3284,16 +3821,16 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="CR8" t="n">
         <v>0</v>
@@ -3302,135 +3839,201 @@
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="CW8" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
+        <v>83</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>20</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>38</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>115</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>116</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>175</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>94</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>103</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>89</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>124</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>124</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>35</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2942</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2876</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2559</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2959</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2606</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2808</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2572</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2727</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2564</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2602</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2714</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1830</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1831</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1745</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1884</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1312</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1763</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>979</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3445,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>706</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3466,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3475,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -3484,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -3541,22 +4144,22 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>1021</v>
+        <v>196</v>
       </c>
       <c r="BS9" t="n">
-        <v>1032</v>
+        <v>44</v>
       </c>
       <c r="BT9" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -3565,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -3586,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
@@ -3595,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -3607,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
@@ -3628,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
@@ -3649,27 +4252,93 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>2238</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>2562</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>2559</v>
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -3684,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3762,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -3930,10 +4599,10 @@
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -3963,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
@@ -3993,12 +4662,78 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -4010,16 +4745,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4028,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -4040,262 +4775,262 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1605</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2394</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2224</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2404</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2294</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2680</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1821</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2211</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2961</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2530</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>798</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>1894</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>2870</v>
+        <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>2640</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2974</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>1979</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>1967</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="BW11" t="n">
-        <v>2056</v>
+        <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>2484</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>2426</v>
+        <v>0</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2430</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>2408</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>1103</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>1248</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>1929</v>
+        <v>0</v>
       </c>
       <c r="CF11" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="CG11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>1501</v>
+        <v>0</v>
       </c>
       <c r="CI11" t="n">
-        <v>2408</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>2766</v>
+        <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>2968</v>
+        <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>2901</v>
+        <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>1098</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>2532</v>
+        <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="CR11" t="n">
-        <v>2486</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
-        <v>878</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>2340</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>1767</v>
+        <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>1207</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
         <v>0</v>
@@ -4313,350 +5048,482 @@
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>517</v>
+        <v>1</v>
       </c>
       <c r="DC11" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>404</v>
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2765</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2560</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2962</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2178</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2938</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2929</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2802</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2238</v>
+      </c>
+      <c r="S12" t="n">
+        <v>501</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2708</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2744</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2197</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2591</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2717</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1674</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1711</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1843</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1763</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1772</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1028</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>983</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>457</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>763</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>98</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>746</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>333</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>725</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>344</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>678</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>210</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>287</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1044</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1110</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>946</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>965</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>495</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>496</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>671</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>845</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>238</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>350</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>703</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>2970</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>2184</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>2569</v>
+      </c>
+      <c r="DZ12" t="n">
         <v>3000</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>146</v>
-      </c>
-      <c r="L12" t="n">
-        <v>192</v>
-      </c>
-      <c r="M12" t="n">
-        <v>428</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2481</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>436</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>963</v>
-      </c>
-      <c r="T12" t="n">
-        <v>867</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1630</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1161</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>59</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>92</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>494</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>234</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>501</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>197</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1998</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>805</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>94</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>1735</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>917</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>1072</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>119</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>113</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>423</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>503</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>20</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>13</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>57</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>208</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>369</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>516</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>67</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>299</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>104</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>481</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>775</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>1770</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>195</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>37</v>
+      <c r="EA12" t="n">
+        <v>2473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -4671,13 +5538,13 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4773,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -4785,19 +5652,19 @@
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -4857,10 +5724,10 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -4878,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
@@ -4941,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="CR13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
@@ -4980,12 +5847,78 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>523</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -5027,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -5042,273 +5975,1524 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AA14" t="n">
-        <v>220</v>
+        <v>1151</v>
       </c>
       <c r="AB14" t="n">
-        <v>241</v>
+        <v>1142</v>
       </c>
       <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1221</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1532</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1529</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2157</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2237</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>306</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>71</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>522</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2334</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2275</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2615</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1345</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>647</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2976</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1840</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2954</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>270</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>2573</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>626</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>486</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>2625</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>2956</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>940</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>780</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>2523</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1948</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>2870</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>2636</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>2039</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>2682</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>2967</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1956</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>1890</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>607</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>625</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>381</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1991</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>2505</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>2358</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>2394</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>1612</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>920</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>823</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1056</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>1969</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>1259</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1416</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1854</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>547</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>2762</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>2969</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>2909</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>1055</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>2520</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>831</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>2413</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>859</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>1732</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>1681</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>1020</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>499</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>385</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1144</v>
+      </c>
+      <c r="C15" t="n">
+        <v>184</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1137</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>191</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>130</v>
+      </c>
+      <c r="P15" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>156</v>
+      </c>
+      <c r="R15" t="n">
+        <v>399</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2106</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>402</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>939</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>833</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1782</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2591</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1078</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2052</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>163</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2255</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2438</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>2126</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>990</v>
-      </c>
-      <c r="BM14" t="n">
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1562</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1068</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>49</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>54</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>92</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>361</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>204</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>960</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>410</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>184</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>205</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>106</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1928</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>40</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>865</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>74</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>1446</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>548</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1046</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>125</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>109</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>415</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>387</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>20</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>53</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>190</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>364</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>413</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>76</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>303</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>75</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>443</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>703</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>2957</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>2833</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>1306</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>1410</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>1013</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>199</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>247</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>6</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>211</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1417</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1868</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>788</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2071</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>145</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2302</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2451</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>67</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>2142</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>941</v>
+      </c>
+      <c r="CG17" t="n">
         <v>130</v>
       </c>
-      <c r="BN14" t="n">
-        <v>289</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>716</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>834</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>2395</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>466</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>375</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>630</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>746</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>157</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>1497</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>2336</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1551</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>1340</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>345</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>1363</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>450</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>860</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC14" t="n">
+      <c r="CH17" t="n">
+        <v>272</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>567</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>597</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>2471</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>487</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>274</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>435</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>784</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>159</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>1457</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>2350</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>1415</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>1179</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>343</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>1290</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>327</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>823</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY17" t="n">
         <v>29</v>
       </c>
-      <c r="DD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE14" t="n">
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
         <v>0</v>
       </c>
     </row>
